--- a/ig/DM-AVRIL-2026/ValueSet-jdv-j352-nature-capacite-finess.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-jdv-j352-nature-capacite-finess.xlsx
@@ -102,7 +102,7 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>natureCapaciteFiness</t>
+    <t>finess</t>
   </si>
   <si>
     <t>=</t>
